--- a/W1D4.xlsx
+++ b/W1D4.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miche\Desktop\Master in Ai Epicode\Esercizi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88004C4-949B-47D7-AFE8-5B9AF35839C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{65B27AD2-36B6-4D16-A1B3-1FB4803AC3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20940" yWindow="0" windowWidth="30765" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="esercizio" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t xml:space="preserve">Esercizio Base </t>
   </si>
@@ -45,9 +46,6 @@
     <t>Esercizio 2</t>
   </si>
   <si>
-    <t>Nella Normale con media 50 e varianza 8 stima la quota di dati tra 48 e 58 (regola 68-95-99.7)</t>
-  </si>
-  <si>
     <t>Esercizio 3</t>
   </si>
   <si>
@@ -72,9 +70,6 @@
     <t>maggiore di 4</t>
   </si>
   <si>
-    <t>4  6</t>
-  </si>
-  <si>
     <t>.3/6</t>
   </si>
   <si>
@@ -96,12 +91,6 @@
     <t xml:space="preserve">delle quote sono inferiori a </t>
   </si>
   <si>
-    <t>Pr(X &lt; 48 )</t>
-  </si>
-  <si>
-    <t>Pr(X &gt; 48)</t>
-  </si>
-  <si>
     <t>Valore</t>
   </si>
   <si>
@@ -154,13 +143,48 @@
   </si>
   <si>
     <t>z-score</t>
+  </si>
+  <si>
+    <t>5 6</t>
+  </si>
+  <si>
+    <t>Nella Normale con media 50 e varianza 8 stima la quota di dati tra 42 e 58 (regola 68-95-99.7)</t>
+  </si>
+  <si>
+    <t>Pr(X &lt; 42 )</t>
+  </si>
+  <si>
+    <t>Pr(X &gt; 42)</t>
+  </si>
+  <si>
+    <r>
+      <t>z=(x-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>μ)/σ</t>
+    </r>
+  </si>
+  <si>
+    <t>Pr(X &lt; 58)</t>
+  </si>
+  <si>
+    <t>Pr(X &gt; 58)</t>
+  </si>
+  <si>
+    <t>Normale Distribuzione</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,16 +192,64 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -185,22 +257,162 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -481,668 +693,502 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{937B3EC1-95FE-4CEA-A554-22738CF3E5CA}">
+  <we:reference id="wa200006518" version="1.2.0.0" store="it-IT" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200006518" version="1.2.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_PYSCRIPT_CODE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_ANACONDA_CODE</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:S29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.5703125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="1" customWidth="1"/>
+    <col min="8" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="29.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="26.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-    </row>
+    </row>
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="24">
+        <f>M11-M10</f>
+        <v>0.68268949213708607</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D10" s="1">
         <v>50</v>
       </c>
-      <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>48</v>
-      </c>
-      <c r="H10" s="1"/>
+        <v>42</v>
+      </c>
       <c r="I10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J10" s="1">
         <f>(G10-$D$10)/$D$11</f>
-        <v>-0.25</v>
-      </c>
-      <c r="K10" s="1"/>
+        <v>-1</v>
+      </c>
       <c r="L10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" s="6">
+        <v>16</v>
+      </c>
+      <c r="M10" s="11">
         <f>_xlfn.NORM.S.DIST(J10,TRUE)</f>
-        <v>0.4012936743170763</v>
+        <v>0.15865525393145699</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O10" s="1">
         <f>G10</f>
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q10" s="6">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="11">
         <f>M10</f>
-        <v>0.4012936743170763</v>
+        <v>0.15865525393145699</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S10" s="6">
+        <v>39</v>
+      </c>
+      <c r="S10" s="12">
         <f>1-Q10</f>
-        <v>0.5987063256829237</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1">
+        <v>0.84134474606854304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9">
         <v>8</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="9">
         <v>58</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="H11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="9">
         <f>(G11-$D$10)/$D$11</f>
         <v>1</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="6">
+      <c r="K11" s="9"/>
+      <c r="L11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="13">
         <f>_xlfn.NORM.S.DIST(J11,TRUE)</f>
         <v>0.84134474606854304</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="N11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" s="9">
         <f>G11</f>
         <v>58</v>
       </c>
-      <c r="P11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="6">
+      <c r="P11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q11" s="13">
         <f>M11</f>
         <v>0.84134474606854304</v>
       </c>
-      <c r="R11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S11" s="6">
+      <c r="R11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="S11" s="14">
         <f>1-Q11</f>
         <v>0.15865525393145696</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-    </row>
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1">
         <v>50</v>
       </c>
-      <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1">
         <v>66</v>
       </c>
-      <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J14" s="1">
         <f>(G14-$D$14)/$D$15</f>
         <v>2</v>
       </c>
-      <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" s="6">
+        <v>16</v>
+      </c>
+      <c r="M14" s="11">
         <f>_xlfn.NORM.S.DIST(J14,TRUE)</f>
         <v>0.97724986805182079</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O14" s="1">
         <f>G14</f>
         <v>66</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q14" s="6">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="11">
         <f>M14</f>
         <v>0.97724986805182079</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="S14" s="6">
+        <v>21</v>
+      </c>
+      <c r="S14" s="12">
         <f>1-Q14</f>
         <v>2.2750131948179209E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="1">
+    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="9">
         <v>8</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="15"/>
+    </row>
+    <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D18" s="1">
         <v>40</v>
       </c>
-      <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="9">
+        <v>12</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="1">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6">
         <v>0.5</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="6">
         <v>0.5</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="7">
         <f>F23*E23</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="6">
         <v>0.83333333333333337</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="6">
         <v>0.83333333333333337</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="7">
         <v>0.69444444444444442</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="2">
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="16">
         <f>1-(25/36)</f>
         <v>0.30555555555555558</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29">
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="9">
         <v>1.5</v>
       </c>
-      <c r="F29" s="4">
+      <c r="E29" s="9"/>
+      <c r="F29" s="14">
         <f>_xlfn.NORM.S.DIST(D29,TRUE)</f>
         <v>0.93319279873114191</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>